--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-Small-3.2-24B-Instruct-2506/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-Small-3.2-24B-Instruct-2506/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D2">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H3">
         <v>426</v>
